--- a/src/nodes/P/compressor_blade_self_frequency.xlsx
+++ b/src/nodes/P/compressor_blade_self_frequency.xlsx
@@ -543,58 +543,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>40.931921502969651</v>
+        <v>47.558047701822915</v>
       </c>
       <c r="C3">
-        <v>256.53448794368177</v>
+        <v>298.0627091719403</v>
       </c>
       <c r="D3">
-        <v>718.37625228878755</v>
+        <v>834.668171435056</v>
       </c>
       <c r="E3">
-        <v>1408.7857783066534</v>
+        <v>1636.8423173462963</v>
       </c>
       <c r="F3">
-        <v>2327.8683057877765</v>
+        <v>2704.7074230850544</v>
       </c>
       <c r="G3">
-        <v>3476.5386722737312</v>
+        <v>4039.3264215859208</v>
       </c>
       <c r="H3">
-        <v>262.31049681675745</v>
+        <v>314.58865354848581</v>
       </c>
       <c r="I3">
-        <v>786.93149045027224</v>
+        <v>943.76596064545743</v>
       </c>
       <c r="J3">
-        <v>1311.5524840837873</v>
+        <v>1572.9432677424293</v>
       </c>
       <c r="K3">
-        <v>1836.1734777173022</v>
+        <v>2202.1205748394009</v>
       </c>
       <c r="L3">
-        <v>2360.7944713508168</v>
+        <v>2831.2978819363721</v>
       </c>
       <c r="M3">
-        <v>2885.4154649843317</v>
+        <v>3460.4751890333441</v>
       </c>
       <c r="N3">
-        <v>524.6209936335149</v>
+        <v>629.17730709697162</v>
       </c>
       <c r="O3">
-        <v>1049.2419872670298</v>
+        <v>1258.3546141939432</v>
       </c>
       <c r="P3">
-        <v>1573.8629809005445</v>
+        <v>1887.5319212909149</v>
       </c>
       <c r="Q3">
-        <v>2098.4839745340596</v>
+        <v>2516.7092283878865</v>
       </c>
       <c r="R3">
-        <v>2623.1049681675745</v>
+        <v>3145.8865354848585</v>
       </c>
       <c r="S3">
-        <v>3147.7259618010889</v>
+        <v>3775.0638425818297</v>
       </c>
     </row>
   </sheetData>

--- a/src/nodes/P/compressor_blade_self_frequency.xlsx
+++ b/src/nodes/P/compressor_blade_self_frequency.xlsx
@@ -604,9 +604,263 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor2</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor3</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor4</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor5</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor6</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage3</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage4</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage5</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>40.521436948085061</v>
+      </c>
+      <c r="C3">
+        <v>253.96183947692293</v>
+      </c>
+      <c r="D3">
+        <v>711.17203745272047</v>
+      </c>
+      <c r="E3">
+        <v>1394.6578121154255</v>
+      </c>
+      <c r="F3">
+        <v>2304.5233478614327</v>
+      </c>
+      <c r="G3">
+        <v>3441.674307811295</v>
+      </c>
+      <c r="H3">
+        <v>224.76511671652992</v>
+      </c>
+      <c r="I3">
+        <v>674.29535014958969</v>
+      </c>
+      <c r="J3">
+        <v>1123.8255835826494</v>
+      </c>
+      <c r="K3">
+        <v>1573.3558170157094</v>
+      </c>
+      <c r="L3">
+        <v>2022.8860504487689</v>
+      </c>
+      <c r="M3">
+        <v>2472.4162838818288</v>
+      </c>
+      <c r="N3">
+        <v>449.53023343305983</v>
+      </c>
+      <c r="O3">
+        <v>899.06046686611967</v>
+      </c>
+      <c r="P3">
+        <v>1348.5907002991794</v>
+      </c>
+      <c r="Q3">
+        <v>1798.1209337322393</v>
+      </c>
+      <c r="R3">
+        <v>2247.6511671652988</v>
+      </c>
+      <c r="S3">
+        <v>2697.1814005983588</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
